--- a/GPIpuget/project/Address.xlsx
+++ b/GPIpuget/project/Address.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="385">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -76,10 +76,7 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
+    <t>No missing bio or symbol files...</t>
   </si>
   <si>
     <t>Missing Nets</t>
@@ -233,6 +230,15 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
+</t>
+  </si>
+  <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
@@ -1061,22 +1067,19 @@
     <t>dbuf</t>
   </si>
   <si>
+    <t>vbuffer</t>
+  </si>
+  <si>
+    <t>nor2</t>
+  </si>
+  <si>
+    <t>delayfixed</t>
+  </si>
+  <si>
+    <t>amux8</t>
+  </si>
+  <si>
     <t>PEBBLEtielo</t>
-  </si>
-  <si>
-    <t>vbuffer</t>
-  </si>
-  <si>
-    <t>nor2</t>
-  </si>
-  <si>
-    <t>delayfixed</t>
-  </si>
-  <si>
-    <t>amux8</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi</t>
   </si>
   <si>
     <t>PAD REPORT</t>
@@ -1585,7 +1588,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1605,7 +1608,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1625,7 +1628,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1640,7 +1643,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1655,7 +1658,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1675,12 +1678,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1695,12 +1698,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1715,12 +1718,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1735,7 +1738,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1750,131 +1753,136 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
         <v>57</v>
       </c>
     </row>
@@ -3503,7 +3511,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3601,7 +3609,7 @@
         <v>334</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>312</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3633,14 +3641,6 @@
         <v>338</v>
       </c>
       <c r="B18" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>339</v>
-      </c>
-      <c r="B19" t="s">
         <v>312</v>
       </c>
     </row>
@@ -3656,85 +3656,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B5" t="s">
         <v>345</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>346</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>347</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>348</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>349</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>350</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>351</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
+        <v>346</v>
+      </c>
+      <c r="J5" t="s">
         <v>352</v>
       </c>
-      <c r="I5" t="s">
-        <v>347</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
+        <v>349</v>
+      </c>
+      <c r="L5" t="s">
         <v>353</v>
       </c>
-      <c r="K5" t="s">
-        <v>350</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>354</v>
-      </c>
-      <c r="M5" t="s">
-        <v>355</v>
       </c>
       <c r="N5" t="s">
         <v>72</v>
       </c>
       <c r="O5" t="s">
+        <v>355</v>
+      </c>
+      <c r="P5" t="s">
         <v>356</v>
       </c>
-      <c r="P5" t="s">
-        <v>357</v>
-      </c>
       <c r="Q5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="R5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -3744,7 +3744,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -3760,11 +3760,6 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3779,22 +3774,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -3809,22 +3804,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -3839,7 +3834,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3849,34 +3844,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>365</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -3891,7 +3886,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3901,34 +3896,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>365</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -3943,22 +3938,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -3973,7 +3968,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -3988,7 +3983,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -4003,7 +3998,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4018,12 +4013,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4038,7 +4033,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4053,7 +4048,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4068,7 +4063,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4078,22 +4073,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -4108,7 +4103,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4123,7 +4118,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4138,7 +4133,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4148,7 +4143,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -4163,7 +4158,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4173,7 +4168,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -4188,7 +4183,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4198,7 +4193,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -4213,7 +4208,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4223,7 +4218,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -4238,7 +4233,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Address.xlsx
+++ b/GPIpuget/project/Address.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="387">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -76,7 +76,10 @@
     <t>Missing Bio Symbol Files</t>
   </si>
   <si>
-    <t>No missing bio or symbol files...</t>
+    <t>PEBBLEtiehi.bio</t>
+  </si>
+  <si>
+    <t>PEBBLEtiehi.v</t>
   </si>
   <si>
     <t>Missing Nets</t>
@@ -231,10 +234,10 @@
   </si>
   <si>
     <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a1['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: can not select part of scalar: a1
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: can not select part of scalar: a1
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
 4 error(s) during elaboration.
 </t>
   </si>
@@ -1067,6 +1070,9 @@
     <t>dbuf</t>
   </si>
   <si>
+    <t>PEBBLEtielo</t>
+  </si>
+  <si>
     <t>vbuffer</t>
   </si>
   <si>
@@ -1079,7 +1085,7 @@
     <t>amux8</t>
   </si>
   <si>
-    <t>PEBBLEtielo</t>
+    <t>PEBBLEtiehi</t>
   </si>
   <si>
     <t>PAD REPORT</t>
@@ -1588,7 +1594,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1608,7 +1614,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1628,7 +1634,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1643,7 +1649,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1658,7 +1664,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1678,12 +1684,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1698,12 +1704,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1718,12 +1724,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1738,7 +1744,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1758,132 +1764,132 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1898,7 +1904,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1943,17 +1949,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1968,7 +1974,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1988,17 +1994,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2013,17 +2019,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2038,81 +2044,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" t="s">
         <v>73</v>
-      </c>
-      <c r="B6" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" t="s">
         <v>76</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
         <v>81</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2120,185 +2126,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2306,445 +2312,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B43" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B46" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B48" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B51" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B54" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B55" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B63" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B66" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B67" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B68" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B69" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B76" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B78" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B79" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B80" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B83" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B84" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B85" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B86" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B87" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B88" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B89" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B90" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B91" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B92" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B93" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B94" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B95" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B96" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B97" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B98" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B99" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2752,628 +2758,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B101" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B102" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B105" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B106" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B107" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B108" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B109" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B110" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B111" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B112" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B115" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B116" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B117" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B118" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B119" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B120" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B121" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B122" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B123" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B124" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B125" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B126" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B127" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B128" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B129" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B130" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B131" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B132" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B133" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B134" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B135" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B136" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B137" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B138" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B139" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B140" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B141" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B142" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B143" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B144" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B145" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B146" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B147" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B148" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B149" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B150" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B151" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B152" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B153" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B154" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B155" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B156" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B157" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B158" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B159" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B160" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B161" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B162" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B163" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B164" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B165" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B166" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B167" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B168" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B169" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B170" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B171" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B172" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B173" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B174" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B175" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B176" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B177" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B178" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B179" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3388,47 +3394,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3436,15 +3442,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3452,7 +3458,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -3467,7 +3473,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -3482,26 +3488,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -3511,12 +3517,12 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3526,122 +3532,130 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B14" t="s">
-        <v>312</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B16" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B17" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B18" t="s">
-        <v>312</v>
+        <v>313</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>340</v>
+      </c>
+      <c r="B19" t="s">
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -3656,85 +3670,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E5" t="s">
+        <v>350</v>
+      </c>
+      <c r="F5" t="s">
+        <v>351</v>
+      </c>
+      <c r="G5" t="s">
+        <v>352</v>
+      </c>
+      <c r="H5" t="s">
+        <v>353</v>
+      </c>
+      <c r="I5" t="s">
         <v>348</v>
       </c>
-      <c r="F5" t="s">
-        <v>349</v>
-      </c>
-      <c r="G5" t="s">
-        <v>350</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
+        <v>354</v>
+      </c>
+      <c r="K5" t="s">
         <v>351</v>
       </c>
-      <c r="I5" t="s">
-        <v>346</v>
-      </c>
-      <c r="J5" t="s">
-        <v>352</v>
-      </c>
-      <c r="K5" t="s">
-        <v>349</v>
-      </c>
       <c r="L5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="R5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -3744,7 +3758,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -3760,6 +3774,11 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3774,22 +3793,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -3804,22 +3823,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -3834,44 +3853,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3886,44 +3905,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3938,22 +3957,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -3968,7 +3987,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -3983,7 +4002,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -3998,12 +4017,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4013,12 +4032,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4033,7 +4052,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -4048,7 +4067,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -4063,7 +4082,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4073,22 +4092,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -4103,12 +4122,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4118,7 +4137,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4133,7 +4152,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4143,7 +4162,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -4158,7 +4177,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4168,7 +4187,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -4183,7 +4202,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4193,7 +4212,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -4208,7 +4227,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4218,7 +4237,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -4233,7 +4252,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Address.xlsx
+++ b/GPIpuget/project/Address.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="385">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -61,10 +61,10 @@
     <t>0</t>
   </si>
   <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>Your schematic contains no net zero.</t>
+    <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
   </si>
   <si>
     <t>Validate no "text" in Datamaps</t>
@@ -86,9 +86,6 @@
   </si>
   <si>
     <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -233,15 +230,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: can not select part of scalar: a1
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: can not select part of scalar: a1
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
-</t>
-  </si>
-  <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
@@ -1049,10 +1037,10 @@
     <t>14</t>
   </si>
   <si>
+    <t>noconn</t>
+  </si>
+  <si>
     <t>nand2</t>
-  </si>
-  <si>
-    <t>noconn</t>
   </si>
   <si>
     <t>wrapper</t>
@@ -1594,7 +1582,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1614,7 +1602,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1634,7 +1622,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1649,7 +1637,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1664,7 +1652,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1684,12 +1672,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1704,12 +1692,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1724,12 +1712,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1744,7 +1732,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1759,137 +1747,132 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1904,7 +1887,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1949,17 +1932,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1974,7 +1957,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1994,17 +1977,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2019,17 +2002,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2044,81 +2027,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2126,185 +2109,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2312,445 +2295,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B43" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B46" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B48" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B50" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B51" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B54" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B55" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B63" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B66" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B67" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B76" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B78" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B79" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B80" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B82" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B83" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B84" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B85" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B86" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B87" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B88" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B89" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B90" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B91" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B92" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B93" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B94" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B95" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B96" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B97" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B98" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B99" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2758,628 +2741,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B101" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B102" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B105" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B106" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B107" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B108" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B109" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B110" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B111" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B112" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B115" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B116" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B117" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B118" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B119" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B120" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B121" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B122" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B123" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B124" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B125" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B126" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B127" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B128" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B129" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B130" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B131" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B132" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B133" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B134" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B135" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B136" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B137" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B138" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B139" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B140" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B141" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B142" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B143" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B144" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B145" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B146" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B147" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B148" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B149" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B150" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B151" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B152" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B153" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B154" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B155" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B156" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B157" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B158" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B159" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B160" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B161" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B162" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B163" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B164" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B165" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B166" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B167" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B168" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B169" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B170" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B171" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B172" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B173" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B174" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B175" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B176" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B177" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B178" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B179" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3394,47 +3377,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>313</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3442,15 +3425,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3458,7 +3441,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -3473,7 +3456,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3488,26 +3471,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -3522,7 +3505,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3532,130 +3515,130 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>311</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B10" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B11" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B15" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B16" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B17" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B18" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B19" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3670,85 +3653,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>345</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C5" t="s">
         <v>346</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>347</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>348</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>349</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>350</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>351</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
+        <v>346</v>
+      </c>
+      <c r="J5" t="s">
         <v>352</v>
       </c>
-      <c r="H5" t="s">
+      <c r="K5" t="s">
+        <v>349</v>
+      </c>
+      <c r="L5" t="s">
         <v>353</v>
       </c>
-      <c r="I5" t="s">
-        <v>348</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
         <v>354</v>
       </c>
-      <c r="K5" t="s">
-        <v>351</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="N5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O5" t="s">
         <v>355</v>
       </c>
-      <c r="M5" t="s">
+      <c r="P5" t="s">
         <v>356</v>
       </c>
-      <c r="N5" t="s">
-        <v>73</v>
-      </c>
-      <c r="O5" t="s">
-        <v>357</v>
-      </c>
-      <c r="P5" t="s">
-        <v>358</v>
-      </c>
       <c r="Q5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="R5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -3793,22 +3776,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -3823,22 +3806,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -3853,44 +3836,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3905,44 +3888,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3957,22 +3940,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -3987,7 +3970,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -4002,7 +3985,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -4017,12 +4000,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4032,12 +4015,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4052,7 +4035,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4067,7 +4050,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4097,17 +4080,17 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -4122,12 +4105,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4137,7 +4120,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4152,7 +4135,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4162,7 +4145,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -4177,7 +4160,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4187,7 +4170,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -4202,7 +4185,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4212,7 +4195,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -4227,7 +4210,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4237,7 +4220,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -4252,7 +4235,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Address.xlsx
+++ b/GPIpuget/project/Address.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="386">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -227,6 +227,15 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
 </t>
   </si>
   <si>
@@ -1747,7 +1756,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1873,6 +1882,11 @@
     <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1887,7 +1901,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1932,17 +1946,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1957,7 +1971,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1977,17 +1991,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2002,17 +2016,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2027,81 +2041,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
         <v>72</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" t="s">
         <v>75</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
         <v>80</v>
-      </c>
-      <c r="B11" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2109,185 +2123,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2295,445 +2309,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B50" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B54" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B63" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B66" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B67" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B68" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B69" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B79" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B80" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B81" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B82" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B83" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B84" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B85" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B86" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B87" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B88" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B89" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B90" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B92" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B93" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B94" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B95" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B96" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B97" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B98" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B99" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2741,628 +2755,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B101" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B102" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B105" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B106" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B107" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B108" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B109" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B110" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B111" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B112" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B116" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B117" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B118" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B119" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B120" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B121" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B122" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B123" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B124" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B125" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B126" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B127" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B128" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B129" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B130" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B131" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B132" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B133" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B134" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B135" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B136" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B137" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B138" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B139" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B140" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B141" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B142" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B143" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B144" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B145" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B146" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B147" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B148" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B149" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B150" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B151" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B152" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B153" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B154" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B155" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B156" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B157" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B158" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B159" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B160" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B161" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B162" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B163" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B164" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B165" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B166" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B167" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B168" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B169" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B170" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B171" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B172" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B173" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B174" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B175" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B176" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B177" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B178" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B179" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3377,47 +3391,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3425,15 +3439,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3441,7 +3455,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3456,7 +3470,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -3471,26 +3485,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -3505,7 +3519,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3515,130 +3529,130 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B15" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B17" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B18" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B19" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -3653,85 +3667,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D5" t="s">
+        <v>348</v>
+      </c>
+      <c r="E5" t="s">
+        <v>349</v>
+      </c>
+      <c r="F5" t="s">
+        <v>350</v>
+      </c>
+      <c r="G5" t="s">
+        <v>351</v>
+      </c>
+      <c r="H5" t="s">
+        <v>352</v>
+      </c>
+      <c r="I5" t="s">
         <v>347</v>
       </c>
-      <c r="E5" t="s">
-        <v>348</v>
-      </c>
-      <c r="F5" t="s">
-        <v>349</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="J5" t="s">
+        <v>353</v>
+      </c>
+      <c r="K5" t="s">
         <v>350</v>
       </c>
-      <c r="H5" t="s">
-        <v>351</v>
-      </c>
-      <c r="I5" t="s">
-        <v>346</v>
-      </c>
-      <c r="J5" t="s">
-        <v>352</v>
-      </c>
-      <c r="K5" t="s">
-        <v>349</v>
-      </c>
       <c r="L5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="R5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -3776,22 +3790,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -3806,22 +3820,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>
@@ -3836,44 +3850,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -3888,44 +3902,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -3940,22 +3954,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -3970,7 +3984,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -3985,7 +3999,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -4000,12 +4014,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4015,12 +4029,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4035,7 +4049,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4050,7 +4064,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -4105,12 +4119,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4120,7 +4134,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>

--- a/GPIpuget/project/Address.xlsx
+++ b/GPIpuget/project/Address.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="385">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -227,15 +227,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:261: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:262: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
 </t>
   </si>
   <si>
@@ -1756,7 +1747,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1882,11 +1873,6 @@
     <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1901,7 +1887,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1946,17 +1932,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1971,7 +1957,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1991,17 +1977,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2016,17 +2002,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2041,81 +2027,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s">
         <v>71</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" t="s">
         <v>74</v>
-      </c>
-      <c r="B7" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" t="s">
         <v>77</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" t="s">
         <v>79</v>
-      </c>
-      <c r="B10" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2123,185 +2109,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" t="s">
         <v>96</v>
-      </c>
-      <c r="B29" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" t="s">
         <v>101</v>
-      </c>
-      <c r="B33" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" t="s">
         <v>103</v>
-      </c>
-      <c r="B34" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" t="s">
         <v>105</v>
-      </c>
-      <c r="B35" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" t="s">
         <v>107</v>
-      </c>
-      <c r="B36" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2309,445 +2295,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" t="s">
         <v>115</v>
-      </c>
-      <c r="B43" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" t="s">
         <v>118</v>
-      </c>
-      <c r="B46" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
+        <v>120</v>
+      </c>
+      <c r="B48" t="s">
         <v>121</v>
-      </c>
-      <c r="B48" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
+        <v>124</v>
+      </c>
+      <c r="B51" t="s">
         <v>125</v>
-      </c>
-      <c r="B51" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" t="s">
         <v>128</v>
-      </c>
-      <c r="B54" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
+        <v>129</v>
+      </c>
+      <c r="B55" t="s">
         <v>130</v>
-      </c>
-      <c r="B55" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
+        <v>137</v>
+      </c>
+      <c r="B63" t="s">
         <v>138</v>
-      </c>
-      <c r="B63" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
+        <v>141</v>
+      </c>
+      <c r="B66" t="s">
         <v>142</v>
-      </c>
-      <c r="B66" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
+        <v>143</v>
+      </c>
+      <c r="B67" t="s">
         <v>144</v>
-      </c>
-      <c r="B67" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B76" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
+        <v>155</v>
+      </c>
+      <c r="B79" t="s">
         <v>156</v>
-      </c>
-      <c r="B79" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B80" t="s">
         <v>158</v>
-      </c>
-      <c r="B80" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B83" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B85" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B86" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B87" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B88" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
+        <v>167</v>
+      </c>
+      <c r="B89" t="s">
         <v>168</v>
-      </c>
-      <c r="B89" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B90" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B91" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B92" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B93" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B94" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B95" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B96" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B97" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B98" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B99" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2755,628 +2741,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B101" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B102" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
+        <v>183</v>
+      </c>
+      <c r="B105" t="s">
         <v>184</v>
-      </c>
-      <c r="B105" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
+        <v>185</v>
+      </c>
+      <c r="B106" t="s">
         <v>186</v>
-      </c>
-      <c r="B106" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
+        <v>187</v>
+      </c>
+      <c r="B107" t="s">
         <v>188</v>
-      </c>
-      <c r="B107" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
+        <v>189</v>
+      </c>
+      <c r="B108" t="s">
         <v>190</v>
-      </c>
-      <c r="B108" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
+        <v>191</v>
+      </c>
+      <c r="B109" t="s">
         <v>192</v>
-      </c>
-      <c r="B109" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
+        <v>193</v>
+      </c>
+      <c r="B110" t="s">
         <v>194</v>
-      </c>
-      <c r="B110" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
+        <v>195</v>
+      </c>
+      <c r="B111" t="s">
         <v>196</v>
-      </c>
-      <c r="B111" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B112" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B115" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
+        <v>200</v>
+      </c>
+      <c r="B116" t="s">
         <v>201</v>
-      </c>
-      <c r="B116" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
+        <v>202</v>
+      </c>
+      <c r="B117" t="s">
         <v>203</v>
-      </c>
-      <c r="B117" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
+        <v>204</v>
+      </c>
+      <c r="B118" t="s">
         <v>205</v>
-      </c>
-      <c r="B118" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
+        <v>206</v>
+      </c>
+      <c r="B119" t="s">
         <v>207</v>
-      </c>
-      <c r="B119" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
+        <v>208</v>
+      </c>
+      <c r="B120" t="s">
         <v>209</v>
-      </c>
-      <c r="B120" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
+        <v>210</v>
+      </c>
+      <c r="B121" t="s">
         <v>211</v>
-      </c>
-      <c r="B121" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B122" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B123" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B124" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
+        <v>215</v>
+      </c>
+      <c r="B125" t="s">
         <v>216</v>
-      </c>
-      <c r="B125" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
+        <v>217</v>
+      </c>
+      <c r="B126" t="s">
         <v>218</v>
-      </c>
-      <c r="B126" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
+        <v>219</v>
+      </c>
+      <c r="B127" t="s">
         <v>220</v>
-      </c>
-      <c r="B127" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
+        <v>221</v>
+      </c>
+      <c r="B128" t="s">
         <v>222</v>
-      </c>
-      <c r="B128" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
+        <v>223</v>
+      </c>
+      <c r="B129" t="s">
         <v>224</v>
-      </c>
-      <c r="B129" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B130" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B131" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B132" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B133" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B134" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
+        <v>230</v>
+      </c>
+      <c r="B135" t="s">
         <v>231</v>
-      </c>
-      <c r="B135" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
+        <v>232</v>
+      </c>
+      <c r="B136" t="s">
         <v>233</v>
-      </c>
-      <c r="B136" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
+        <v>234</v>
+      </c>
+      <c r="B137" t="s">
         <v>235</v>
-      </c>
-      <c r="B137" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
+        <v>236</v>
+      </c>
+      <c r="B138" t="s">
         <v>237</v>
-      </c>
-      <c r="B138" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
+        <v>238</v>
+      </c>
+      <c r="B139" t="s">
         <v>239</v>
-      </c>
-      <c r="B139" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B140" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B141" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B142" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B143" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B144" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B145" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B146" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B147" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
+        <v>248</v>
+      </c>
+      <c r="B148" t="s">
         <v>249</v>
-      </c>
-      <c r="B148" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
+        <v>250</v>
+      </c>
+      <c r="B149" t="s">
         <v>251</v>
-      </c>
-      <c r="B149" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
+        <v>252</v>
+      </c>
+      <c r="B150" t="s">
         <v>253</v>
-      </c>
-      <c r="B150" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
+        <v>254</v>
+      </c>
+      <c r="B151" t="s">
         <v>255</v>
-      </c>
-      <c r="B151" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
+        <v>256</v>
+      </c>
+      <c r="B152" t="s">
         <v>257</v>
-      </c>
-      <c r="B152" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
+        <v>258</v>
+      </c>
+      <c r="B153" t="s">
         <v>259</v>
-      </c>
-      <c r="B153" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
+        <v>260</v>
+      </c>
+      <c r="B154" t="s">
         <v>261</v>
-      </c>
-      <c r="B154" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
+        <v>262</v>
+      </c>
+      <c r="B155" t="s">
         <v>263</v>
-      </c>
-      <c r="B155" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
+        <v>264</v>
+      </c>
+      <c r="B156" t="s">
         <v>265</v>
-      </c>
-      <c r="B156" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
+        <v>266</v>
+      </c>
+      <c r="B157" t="s">
         <v>267</v>
-      </c>
-      <c r="B157" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
+        <v>268</v>
+      </c>
+      <c r="B158" t="s">
         <v>269</v>
-      </c>
-      <c r="B158" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
+        <v>270</v>
+      </c>
+      <c r="B159" t="s">
         <v>271</v>
-      </c>
-      <c r="B159" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
+        <v>272</v>
+      </c>
+      <c r="B160" t="s">
         <v>273</v>
-      </c>
-      <c r="B160" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
+        <v>274</v>
+      </c>
+      <c r="B161" t="s">
         <v>275</v>
-      </c>
-      <c r="B161" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
+        <v>276</v>
+      </c>
+      <c r="B162" t="s">
         <v>277</v>
-      </c>
-      <c r="B162" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
+        <v>278</v>
+      </c>
+      <c r="B163" t="s">
         <v>279</v>
-      </c>
-      <c r="B163" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
+        <v>280</v>
+      </c>
+      <c r="B164" t="s">
         <v>281</v>
-      </c>
-      <c r="B164" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B165" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B166" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B167" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
+        <v>285</v>
+      </c>
+      <c r="B168" t="s">
         <v>286</v>
-      </c>
-      <c r="B168" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
+        <v>287</v>
+      </c>
+      <c r="B169" t="s">
         <v>288</v>
-      </c>
-      <c r="B169" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
+        <v>289</v>
+      </c>
+      <c r="B170" t="s">
         <v>290</v>
-      </c>
-      <c r="B170" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
+        <v>291</v>
+      </c>
+      <c r="B171" t="s">
         <v>292</v>
-      </c>
-      <c r="B171" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
+        <v>293</v>
+      </c>
+      <c r="B172" t="s">
         <v>294</v>
-      </c>
-      <c r="B172" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B173" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B174" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B175" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B176" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B177" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
+        <v>300</v>
+      </c>
+      <c r="B178" t="s">
         <v>301</v>
-      </c>
-      <c r="B178" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B179" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3391,47 +3377,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3439,15 +3425,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3455,7 +3441,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -3470,7 +3456,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3485,26 +3471,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3519,7 +3505,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3529,130 +3515,130 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B5" t="s">
         <v>323</v>
-      </c>
-      <c r="B5" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B6" t="s">
         <v>325</v>
-      </c>
-      <c r="B6" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B15" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B18" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B19" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3667,85 +3653,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>344</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B5" t="s">
         <v>345</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>346</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>347</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>348</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>349</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>350</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>351</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
+        <v>346</v>
+      </c>
+      <c r="J5" t="s">
         <v>352</v>
       </c>
-      <c r="I5" t="s">
-        <v>347</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
+        <v>349</v>
+      </c>
+      <c r="L5" t="s">
         <v>353</v>
       </c>
-      <c r="K5" t="s">
-        <v>350</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>354</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O5" t="s">
         <v>355</v>
       </c>
-      <c r="N5" t="s">
-        <v>72</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>356</v>
       </c>
-      <c r="P5" t="s">
-        <v>357</v>
-      </c>
       <c r="Q5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="R5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -3790,22 +3776,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -3820,22 +3806,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -3850,44 +3836,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -3902,44 +3888,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>371</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -3954,22 +3940,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -3984,7 +3970,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -3999,7 +3985,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -4014,12 +4000,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4029,12 +4015,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4049,7 +4035,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4064,7 +4050,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4119,12 +4105,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4134,7 +4120,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>

--- a/GPIpuget/project/Address.xlsx
+++ b/GPIpuget/project/Address.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="384">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -61,31 +61,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Your schematic contains no net zero.</t>
+  </si>
+  <si>
+    <t>Validate no "text" in Datamaps</t>
+  </si>
+  <si>
+    <t>No errors</t>
+  </si>
+  <si>
+    <t>Missing Bio Symbol Files</t>
+  </si>
+  <si>
+    <t>No missing bio or symbol files...</t>
+  </si>
+  <si>
+    <t>Missing Nets</t>
+  </si>
+  <si>
+    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+  </si>
+  <si>
     <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
-  </si>
-  <si>
-    <t>Validate no "text" in Datamaps</t>
-  </si>
-  <si>
-    <t>No errors</t>
-  </si>
-  <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.bio</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi.v</t>
-  </si>
-  <si>
-    <t>Missing Nets</t>
-  </si>
-  <si>
-    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -1037,10 +1037,13 @@
     <t>14</t>
   </si>
   <si>
+    <t>nand2</t>
+  </si>
+  <si>
     <t>noconn</t>
   </si>
   <si>
-    <t>nand2</t>
+    <t>PEBBLEtielo</t>
   </si>
   <si>
     <t>wrapper</t>
@@ -1058,9 +1061,6 @@
     <t>dbuf</t>
   </si>
   <si>
-    <t>PEBBLEtielo</t>
-  </si>
-  <si>
     <t>vbuffer</t>
   </si>
   <si>
@@ -1071,9 +1071,6 @@
   </si>
   <si>
     <t>amux8</t>
-  </si>
-  <si>
-    <t>PEBBLEtiehi</t>
   </si>
   <si>
     <t>PAD REPORT</t>
@@ -3500,7 +3497,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3542,7 +3539,7 @@
         <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3550,7 +3547,7 @@
         <v>327</v>
       </c>
       <c r="B8" t="s">
-        <v>309</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3558,7 +3555,7 @@
         <v>328</v>
       </c>
       <c r="B9" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3630,14 +3627,6 @@
         <v>337</v>
       </c>
       <c r="B18" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>338</v>
-      </c>
-      <c r="B19" t="s">
         <v>311</v>
       </c>
     </row>
@@ -3653,85 +3642,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
+        <v>343</v>
+      </c>
+      <c r="B5" t="s">
         <v>344</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>345</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>346</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>347</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>348</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>349</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>350</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
+        <v>345</v>
+      </c>
+      <c r="J5" t="s">
         <v>351</v>
       </c>
-      <c r="I5" t="s">
-        <v>346</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
+        <v>348</v>
+      </c>
+      <c r="L5" t="s">
         <v>352</v>
       </c>
-      <c r="K5" t="s">
-        <v>349</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>353</v>
-      </c>
-      <c r="M5" t="s">
-        <v>354</v>
       </c>
       <c r="N5" t="s">
         <v>71</v>
       </c>
       <c r="O5" t="s">
+        <v>354</v>
+      </c>
+      <c r="P5" t="s">
         <v>355</v>
       </c>
-      <c r="P5" t="s">
-        <v>356</v>
-      </c>
       <c r="Q5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="R5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -3741,7 +3730,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -3757,11 +3746,6 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3776,22 +3760,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -3806,22 +3790,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -3836,7 +3820,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3846,34 +3830,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>307</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -3888,7 +3872,7 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3898,34 +3882,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>307</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -3940,22 +3924,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -3970,7 +3954,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -3985,7 +3969,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -4000,7 +3984,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4015,12 +3999,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -4035,7 +4019,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4050,7 +4034,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4065,7 +4049,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4075,12 +4059,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -4105,7 +4089,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4120,7 +4104,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/GPIpuget/project/Address.xlsx
+++ b/GPIpuget/project/Address.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="385">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -227,6 +227,14 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362:        : Padding 6 high bits of the expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369:        : Padding 6 high bits of the expression.
 </t>
   </si>
   <si>
@@ -1744,7 +1752,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1870,6 +1878,11 @@
     <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1884,7 +1897,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1929,17 +1942,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1954,7 +1967,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1974,17 +1987,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1999,17 +2012,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -2024,81 +2037,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
         <v>72</v>
-      </c>
-      <c r="B6" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" t="s">
         <v>75</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
         <v>80</v>
-      </c>
-      <c r="B11" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2106,185 +2119,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2292,445 +2305,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B50" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B54" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B63" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B66" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B67" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B68" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B69" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B79" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B80" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B81" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B82" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B83" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B84" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B85" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B86" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B87" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B88" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B89" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B90" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B92" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B93" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B94" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B95" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B96" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B97" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B98" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B99" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2738,628 +2751,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B101" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B102" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B105" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B106" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B107" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B108" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B109" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B110" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B111" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B112" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B116" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B117" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B118" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B119" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B120" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B121" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B122" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B123" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B124" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B125" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B126" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B127" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B128" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B129" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B130" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B131" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B132" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B133" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B134" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B135" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B136" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B137" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B138" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B139" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B140" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B141" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B142" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B143" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B144" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B145" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B146" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B147" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B148" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B149" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B150" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B151" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B152" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B153" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B154" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B155" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B156" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B157" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B158" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B159" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B160" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B161" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B162" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B163" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B164" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B165" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B166" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B167" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B168" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B169" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B170" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B171" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B172" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B173" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B174" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B175" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B176" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B177" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B178" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B179" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3374,47 +3387,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3422,15 +3435,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3438,7 +3451,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3453,7 +3466,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -3468,26 +3481,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -3502,7 +3515,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3512,122 +3525,122 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B15" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B17" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B18" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -3642,85 +3655,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C5" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D5" t="s">
+        <v>347</v>
+      </c>
+      <c r="E5" t="s">
+        <v>348</v>
+      </c>
+      <c r="F5" t="s">
+        <v>349</v>
+      </c>
+      <c r="G5" t="s">
+        <v>350</v>
+      </c>
+      <c r="H5" t="s">
+        <v>351</v>
+      </c>
+      <c r="I5" t="s">
         <v>346</v>
       </c>
-      <c r="E5" t="s">
-        <v>347</v>
-      </c>
-      <c r="F5" t="s">
-        <v>348</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="J5" t="s">
+        <v>352</v>
+      </c>
+      <c r="K5" t="s">
         <v>349</v>
       </c>
-      <c r="H5" t="s">
-        <v>350</v>
-      </c>
-      <c r="I5" t="s">
-        <v>345</v>
-      </c>
-      <c r="J5" t="s">
-        <v>351</v>
-      </c>
-      <c r="K5" t="s">
-        <v>348</v>
-      </c>
       <c r="L5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="R5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -3760,22 +3773,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -3790,22 +3803,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -3820,44 +3833,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -3872,44 +3885,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -3924,22 +3937,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -3954,7 +3967,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -3969,7 +3982,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -3984,12 +3997,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -3999,12 +4012,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4019,7 +4032,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4034,7 +4047,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4089,12 +4102,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4104,7 +4117,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>

--- a/GPIpuget/project/Address.xlsx
+++ b/GPIpuget/project/Address.xlsx
@@ -231,10 +231,11 @@
   </si>
   <si>
     <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:362:        : Padding 6 high bits of the expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369: warning: Port 1 (q) of PEBBLEtielo expects 1 bits, got 7.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:369:        : Padding 6 high bits of the expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
 </t>
   </si>
   <si>

--- a/GPIpuget/project/Address.xlsx
+++ b/GPIpuget/project/Address.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="384">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -227,15 +227,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `a0['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
 </t>
   </si>
   <si>
@@ -1753,7 +1744,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1879,11 +1870,6 @@
     <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1898,7 +1884,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1943,17 +1929,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1968,7 +1954,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1988,17 +1974,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -2013,17 +1999,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2038,81 +2024,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" t="s">
         <v>71</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" t="s">
         <v>74</v>
-      </c>
-      <c r="B7" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" t="s">
         <v>77</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" t="s">
         <v>79</v>
-      </c>
-      <c r="B10" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2120,185 +2106,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" t="s">
         <v>96</v>
-      </c>
-      <c r="B29" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" t="s">
         <v>101</v>
-      </c>
-      <c r="B33" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" t="s">
         <v>103</v>
-      </c>
-      <c r="B34" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" t="s">
         <v>105</v>
-      </c>
-      <c r="B35" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" t="s">
         <v>107</v>
-      </c>
-      <c r="B36" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2306,445 +2292,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" t="s">
         <v>115</v>
-      </c>
-      <c r="B43" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" t="s">
         <v>118</v>
-      </c>
-      <c r="B46" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
+        <v>120</v>
+      </c>
+      <c r="B48" t="s">
         <v>121</v>
-      </c>
-      <c r="B48" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
+        <v>124</v>
+      </c>
+      <c r="B51" t="s">
         <v>125</v>
-      </c>
-      <c r="B51" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" t="s">
         <v>128</v>
-      </c>
-      <c r="B54" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
+        <v>129</v>
+      </c>
+      <c r="B55" t="s">
         <v>130</v>
-      </c>
-      <c r="B55" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
+        <v>137</v>
+      </c>
+      <c r="B63" t="s">
         <v>138</v>
-      </c>
-      <c r="B63" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
+        <v>141</v>
+      </c>
+      <c r="B66" t="s">
         <v>142</v>
-      </c>
-      <c r="B66" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
+        <v>143</v>
+      </c>
+      <c r="B67" t="s">
         <v>144</v>
-      </c>
-      <c r="B67" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B76" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
+        <v>155</v>
+      </c>
+      <c r="B79" t="s">
         <v>156</v>
-      </c>
-      <c r="B79" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B80" t="s">
         <v>158</v>
-      </c>
-      <c r="B80" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B81" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B83" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B85" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B86" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B87" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B88" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
+        <v>167</v>
+      </c>
+      <c r="B89" t="s">
         <v>168</v>
-      </c>
-      <c r="B89" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B90" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B91" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B92" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B93" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B94" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B95" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B96" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B97" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B98" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B99" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2752,628 +2738,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B101" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B102" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
+        <v>183</v>
+      </c>
+      <c r="B105" t="s">
         <v>184</v>
-      </c>
-      <c r="B105" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
+        <v>185</v>
+      </c>
+      <c r="B106" t="s">
         <v>186</v>
-      </c>
-      <c r="B106" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
+        <v>187</v>
+      </c>
+      <c r="B107" t="s">
         <v>188</v>
-      </c>
-      <c r="B107" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
+        <v>189</v>
+      </c>
+      <c r="B108" t="s">
         <v>190</v>
-      </c>
-      <c r="B108" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
+        <v>191</v>
+      </c>
+      <c r="B109" t="s">
         <v>192</v>
-      </c>
-      <c r="B109" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
+        <v>193</v>
+      </c>
+      <c r="B110" t="s">
         <v>194</v>
-      </c>
-      <c r="B110" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
+        <v>195</v>
+      </c>
+      <c r="B111" t="s">
         <v>196</v>
-      </c>
-      <c r="B111" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B112" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B115" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
+        <v>200</v>
+      </c>
+      <c r="B116" t="s">
         <v>201</v>
-      </c>
-      <c r="B116" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
+        <v>202</v>
+      </c>
+      <c r="B117" t="s">
         <v>203</v>
-      </c>
-      <c r="B117" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
+        <v>204</v>
+      </c>
+      <c r="B118" t="s">
         <v>205</v>
-      </c>
-      <c r="B118" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
+        <v>206</v>
+      </c>
+      <c r="B119" t="s">
         <v>207</v>
-      </c>
-      <c r="B119" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
+        <v>208</v>
+      </c>
+      <c r="B120" t="s">
         <v>209</v>
-      </c>
-      <c r="B120" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
+        <v>210</v>
+      </c>
+      <c r="B121" t="s">
         <v>211</v>
-      </c>
-      <c r="B121" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B122" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B123" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B124" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
+        <v>215</v>
+      </c>
+      <c r="B125" t="s">
         <v>216</v>
-      </c>
-      <c r="B125" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
+        <v>217</v>
+      </c>
+      <c r="B126" t="s">
         <v>218</v>
-      </c>
-      <c r="B126" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
+        <v>219</v>
+      </c>
+      <c r="B127" t="s">
         <v>220</v>
-      </c>
-      <c r="B127" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
+        <v>221</v>
+      </c>
+      <c r="B128" t="s">
         <v>222</v>
-      </c>
-      <c r="B128" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
+        <v>223</v>
+      </c>
+      <c r="B129" t="s">
         <v>224</v>
-      </c>
-      <c r="B129" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B130" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B131" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B132" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B133" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B134" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
+        <v>230</v>
+      </c>
+      <c r="B135" t="s">
         <v>231</v>
-      </c>
-      <c r="B135" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
+        <v>232</v>
+      </c>
+      <c r="B136" t="s">
         <v>233</v>
-      </c>
-      <c r="B136" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
+        <v>234</v>
+      </c>
+      <c r="B137" t="s">
         <v>235</v>
-      </c>
-      <c r="B137" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
+        <v>236</v>
+      </c>
+      <c r="B138" t="s">
         <v>237</v>
-      </c>
-      <c r="B138" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
+        <v>238</v>
+      </c>
+      <c r="B139" t="s">
         <v>239</v>
-      </c>
-      <c r="B139" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B140" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B141" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B142" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B143" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B144" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B145" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B146" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B147" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
+        <v>248</v>
+      </c>
+      <c r="B148" t="s">
         <v>249</v>
-      </c>
-      <c r="B148" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
+        <v>250</v>
+      </c>
+      <c r="B149" t="s">
         <v>251</v>
-      </c>
-      <c r="B149" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
+        <v>252</v>
+      </c>
+      <c r="B150" t="s">
         <v>253</v>
-      </c>
-      <c r="B150" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
+        <v>254</v>
+      </c>
+      <c r="B151" t="s">
         <v>255</v>
-      </c>
-      <c r="B151" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
+        <v>256</v>
+      </c>
+      <c r="B152" t="s">
         <v>257</v>
-      </c>
-      <c r="B152" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
+        <v>258</v>
+      </c>
+      <c r="B153" t="s">
         <v>259</v>
-      </c>
-      <c r="B153" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
+        <v>260</v>
+      </c>
+      <c r="B154" t="s">
         <v>261</v>
-      </c>
-      <c r="B154" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
+        <v>262</v>
+      </c>
+      <c r="B155" t="s">
         <v>263</v>
-      </c>
-      <c r="B155" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
+        <v>264</v>
+      </c>
+      <c r="B156" t="s">
         <v>265</v>
-      </c>
-      <c r="B156" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
+        <v>266</v>
+      </c>
+      <c r="B157" t="s">
         <v>267</v>
-      </c>
-      <c r="B157" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
+        <v>268</v>
+      </c>
+      <c r="B158" t="s">
         <v>269</v>
-      </c>
-      <c r="B158" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
+        <v>270</v>
+      </c>
+      <c r="B159" t="s">
         <v>271</v>
-      </c>
-      <c r="B159" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
+        <v>272</v>
+      </c>
+      <c r="B160" t="s">
         <v>273</v>
-      </c>
-      <c r="B160" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
+        <v>274</v>
+      </c>
+      <c r="B161" t="s">
         <v>275</v>
-      </c>
-      <c r="B161" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
+        <v>276</v>
+      </c>
+      <c r="B162" t="s">
         <v>277</v>
-      </c>
-      <c r="B162" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
+        <v>278</v>
+      </c>
+      <c r="B163" t="s">
         <v>279</v>
-      </c>
-      <c r="B163" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
+        <v>280</v>
+      </c>
+      <c r="B164" t="s">
         <v>281</v>
-      </c>
-      <c r="B164" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B165" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B166" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B167" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
+        <v>285</v>
+      </c>
+      <c r="B168" t="s">
         <v>286</v>
-      </c>
-      <c r="B168" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
+        <v>287</v>
+      </c>
+      <c r="B169" t="s">
         <v>288</v>
-      </c>
-      <c r="B169" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
+        <v>289</v>
+      </c>
+      <c r="B170" t="s">
         <v>290</v>
-      </c>
-      <c r="B170" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
+        <v>291</v>
+      </c>
+      <c r="B171" t="s">
         <v>292</v>
-      </c>
-      <c r="B171" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
+        <v>293</v>
+      </c>
+      <c r="B172" t="s">
         <v>294</v>
-      </c>
-      <c r="B172" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B173" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B174" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B175" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B176" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B177" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
+        <v>300</v>
+      </c>
+      <c r="B178" t="s">
         <v>301</v>
-      </c>
-      <c r="B178" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B179" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3388,47 +3374,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>311</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>312</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3436,15 +3422,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3452,7 +3438,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -3467,7 +3453,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3482,26 +3468,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>307</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3516,7 +3502,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3526,122 +3512,122 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B5" t="s">
         <v>323</v>
-      </c>
-      <c r="B5" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B6" t="s">
         <v>325</v>
-      </c>
-      <c r="B6" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B15" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B16" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B17" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B18" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3656,85 +3642,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>343</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
+        <v>343</v>
+      </c>
+      <c r="B5" t="s">
         <v>344</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>345</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>346</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>347</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>348</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>349</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>350</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
+        <v>345</v>
+      </c>
+      <c r="J5" t="s">
         <v>351</v>
       </c>
-      <c r="I5" t="s">
-        <v>346</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
+        <v>348</v>
+      </c>
+      <c r="L5" t="s">
         <v>352</v>
       </c>
-      <c r="K5" t="s">
-        <v>349</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>353</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O5" t="s">
         <v>354</v>
       </c>
-      <c r="N5" t="s">
-        <v>72</v>
-      </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>355</v>
       </c>
-      <c r="P5" t="s">
-        <v>356</v>
-      </c>
       <c r="Q5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="R5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -3774,22 +3760,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -3804,22 +3790,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -3834,44 +3820,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -3886,44 +3872,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -3938,22 +3924,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -3968,7 +3954,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -3983,7 +3969,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -3998,12 +3984,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4013,12 +3999,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -4033,7 +4019,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4048,7 +4034,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4103,12 +4089,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4118,7 +4104,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/GPIpuget/project/Address.xlsx
+++ b/GPIpuget/project/Address.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="387">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -86,6 +86,12 @@
   </si>
   <si>
     <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XU6,trim_vbuffer_negative</t>
+  </si>
+  <si>
+    <t>XU6,trim_vbuffer_positive</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -227,6 +233,15 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_negative['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_positive['sd6:'sd0]' in `GPIpugetMAIN'
+/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
+4 error(s) during elaboration.
 </t>
   </si>
   <si>
@@ -1579,7 +1594,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1599,7 +1614,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1619,7 +1634,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1634,7 +1649,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1649,7 +1664,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1669,12 +1684,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1689,12 +1704,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1709,12 +1724,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1729,7 +1744,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1744,132 +1759,137 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1884,7 +1904,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1929,17 +1949,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1954,7 +1974,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1974,17 +1994,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1999,17 +2019,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2024,81 +2044,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2106,185 +2126,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B33" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2292,445 +2312,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B40" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B47" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B48" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B49" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B50" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B51" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B54" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B55" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B63" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B66" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B67" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B68" t="s">
         <v>145</v>
-      </c>
-      <c r="B68" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B69" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B79" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B80" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B81" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B82" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B83" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B84" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B85" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B86" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B87" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B88" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B89" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B90" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B92" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B93" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B94" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B95" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B96" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B97" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B98" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B99" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2738,628 +2758,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B101" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B102" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B105" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B106" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B107" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B108" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B109" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B110" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B111" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B112" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B116" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B117" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B118" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B119" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B120" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B121" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B122" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B123" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
+        <v>217</v>
+      </c>
+      <c r="B124" t="s">
         <v>214</v>
-      </c>
-      <c r="B124" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B125" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B126" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B127" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B128" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B129" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B130" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B131" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B132" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B133" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B134" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B135" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B136" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B137" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B138" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B139" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B140" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B141" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B142" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B143" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B144" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B145" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B146" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B147" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B148" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B149" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B150" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B151" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B152" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B153" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B154" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B155" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B156" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B157" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B158" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B159" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B160" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B161" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B162" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B163" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B164" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B165" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B166" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B167" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B168" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B169" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B170" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B171" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B172" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B173" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B174" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B175" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B176" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B177" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B178" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B179" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -3374,47 +3394,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3422,15 +3442,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3438,7 +3458,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -3453,7 +3473,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -3468,26 +3488,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3502,7 +3522,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3512,122 +3532,122 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B5" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B6" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B7" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B11" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B15" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B16" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B17" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B18" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -3642,85 +3662,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E5" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F5" t="s">
+        <v>351</v>
+      </c>
+      <c r="G5" t="s">
+        <v>352</v>
+      </c>
+      <c r="H5" t="s">
+        <v>353</v>
+      </c>
+      <c r="I5" t="s">
         <v>348</v>
       </c>
-      <c r="G5" t="s">
-        <v>349</v>
-      </c>
-      <c r="H5" t="s">
-        <v>350</v>
-      </c>
-      <c r="I5" t="s">
-        <v>345</v>
-      </c>
       <c r="J5" t="s">
+        <v>354</v>
+      </c>
+      <c r="K5" t="s">
         <v>351</v>
       </c>
-      <c r="K5" t="s">
-        <v>348</v>
-      </c>
       <c r="L5" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="M5" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="N5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="O5" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="P5" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q5" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="R5" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -3760,22 +3780,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -3790,22 +3810,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -3820,44 +3840,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3872,44 +3892,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3924,22 +3944,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -3954,7 +3974,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -3969,7 +3989,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -3984,12 +4004,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -3999,12 +4019,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4019,7 +4039,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -4034,7 +4054,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -4044,7 +4064,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -4075,6 +4095,16 @@
     <row r="9" spans="1:1">
       <c r="A9" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -4089,12 +4119,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4104,7 +4134,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -4119,7 +4149,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4129,7 +4159,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -4144,7 +4174,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4154,7 +4184,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -4169,7 +4199,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4179,7 +4209,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -4194,7 +4224,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4204,7 +4234,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -4219,7 +4249,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Address.xlsx
+++ b/GPIpuget/project/Address.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="383">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -61,10 +61,10 @@
     <t>0</t>
   </si>
   <si>
-    <t>Overview</t>
-  </si>
-  <si>
-    <t>Your schematic contains no net zero.</t>
+    <t>XGPI,XMAIN</t>
+  </si>
+  <si>
+    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
   </si>
   <si>
     <t>Validate no "text" in Datamaps</t>
@@ -83,15 +83,6 @@
   </si>
   <si>
     <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XU6,trim_vbuffer_negative</t>
-  </si>
-  <si>
-    <t>XU6,trim_vbuffer_positive</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -236,15 +227,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_negative['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:249: error: Failed to elaborate port expression.
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Unable to bind wire/reg/memory `TBD_XGPI_XMAIN_XU6_trim_vbuffer_positive['sd6:'sd0]' in `GPIpugetMAIN'
-/celera/projects/Sunnyvale/software/GPIpuget/verilog8/GPIpugetMAIN.v:250: error: Failed to elaborate port expression.
-4 error(s) during elaboration.
-</t>
-  </si>
-  <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
@@ -1052,28 +1034,28 @@
     <t>14</t>
   </si>
   <si>
+    <t>noconn</t>
+  </si>
+  <si>
     <t>nand2</t>
   </si>
   <si>
-    <t>noconn</t>
+    <t>wrapper</t>
+  </si>
+  <si>
+    <t>switchpulldown</t>
+  </si>
+  <si>
+    <t>switchgnd</t>
+  </si>
+  <si>
+    <t>nand3</t>
+  </si>
+  <si>
+    <t>dbuf</t>
   </si>
   <si>
     <t>PEBBLEtielo</t>
-  </si>
-  <si>
-    <t>wrapper</t>
-  </si>
-  <si>
-    <t>switchpulldown</t>
-  </si>
-  <si>
-    <t>switchgnd</t>
-  </si>
-  <si>
-    <t>nand3</t>
-  </si>
-  <si>
-    <t>dbuf</t>
   </si>
   <si>
     <t>vbuffer</t>
@@ -1594,7 +1576,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1614,7 +1596,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1634,7 +1616,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1649,7 +1631,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1664,7 +1646,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1684,12 +1666,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1704,12 +1686,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1724,12 +1706,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1744,7 +1726,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1759,137 +1741,132 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1904,7 +1881,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1949,17 +1926,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1974,7 +1951,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1994,17 +1971,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2019,17 +1996,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -2044,81 +2021,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2126,185 +2103,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B29" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B38" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2312,445 +2289,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B47" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B48" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B49" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B50" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B51" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B55" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B63" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B66" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B67" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B68" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B69" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B76" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B77" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B78" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B79" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B80" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B81" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B83" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B84" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B85" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B86" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B87" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B88" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B89" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B90" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B91" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B92" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B93" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B94" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B95" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B96" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B97" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B98" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B99" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2758,628 +2735,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B101" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B102" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B105" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B106" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B107" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B108" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B109" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B110" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B111" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B112" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B115" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B116" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B117" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B118" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B119" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B120" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B121" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B122" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B123" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B124" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B125" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B126" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B127" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B128" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B129" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B130" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B131" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B132" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B133" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B134" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B135" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B136" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B137" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B138" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B139" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B140" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B141" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B142" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B143" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B144" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B145" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B146" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B147" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B148" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B149" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B150" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B151" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B152" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B153" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B154" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B155" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B156" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B157" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B158" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B159" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B160" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B161" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B162" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B163" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B164" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B165" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B166" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B167" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B168" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B169" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B170" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B171" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B172" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B173" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B174" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B175" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B176" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B177" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B178" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B179" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -3394,47 +3371,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="I4" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3442,15 +3419,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3458,7 +3435,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -3473,7 +3450,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -3488,26 +3465,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -3522,7 +3499,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3532,122 +3509,122 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B5" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B7" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B12" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B14" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B15" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B16" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B17" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B18" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -3662,85 +3639,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
+        <v>342</v>
+      </c>
+      <c r="B5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C5" t="s">
+        <v>344</v>
+      </c>
+      <c r="D5" t="s">
+        <v>345</v>
+      </c>
+      <c r="E5" t="s">
         <v>346</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F5" t="s">
         <v>347</v>
       </c>
-      <c r="C5" t="s">
+      <c r="G5" t="s">
         <v>348</v>
       </c>
-      <c r="D5" t="s">
+      <c r="H5" t="s">
         <v>349</v>
       </c>
-      <c r="E5" t="s">
+      <c r="I5" t="s">
+        <v>344</v>
+      </c>
+      <c r="J5" t="s">
         <v>350</v>
       </c>
-      <c r="F5" t="s">
+      <c r="K5" t="s">
+        <v>347</v>
+      </c>
+      <c r="L5" t="s">
         <v>351</v>
       </c>
-      <c r="G5" t="s">
+      <c r="M5" t="s">
         <v>352</v>
       </c>
-      <c r="H5" t="s">
+      <c r="N5" t="s">
+        <v>70</v>
+      </c>
+      <c r="O5" t="s">
         <v>353</v>
       </c>
-      <c r="I5" t="s">
-        <v>348</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="P5" t="s">
         <v>354</v>
       </c>
-      <c r="K5" t="s">
-        <v>351</v>
-      </c>
-      <c r="L5" t="s">
-        <v>355</v>
-      </c>
-      <c r="M5" t="s">
-        <v>356</v>
-      </c>
-      <c r="N5" t="s">
-        <v>74</v>
-      </c>
-      <c r="O5" t="s">
-        <v>357</v>
-      </c>
-      <c r="P5" t="s">
-        <v>358</v>
-      </c>
       <c r="Q5" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="R5" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -3780,22 +3757,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -3810,22 +3787,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -3840,44 +3817,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3892,44 +3869,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -3944,22 +3921,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -3974,7 +3951,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -3989,7 +3966,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -4004,12 +3981,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4019,12 +3996,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -4039,7 +4016,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -4054,7 +4031,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4064,7 +4041,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -4084,27 +4061,17 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -4119,12 +4086,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4134,7 +4101,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -4149,7 +4116,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4159,7 +4126,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -4174,7 +4141,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4184,7 +4151,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -4199,7 +4166,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4209,7 +4176,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -4224,7 +4191,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4234,7 +4201,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -4249,7 +4216,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Address.xlsx
+++ b/GPIpuget/project/Address.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="384">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -61,28 +61,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>Your schematic contains no net zero.</t>
+  </si>
+  <si>
+    <t>Validate no "text" in Datamaps</t>
+  </si>
+  <si>
+    <t>No errors</t>
+  </si>
+  <si>
+    <t>Missing Bio Symbol Files</t>
+  </si>
+  <si>
+    <t>No missing bio or symbol files...</t>
+  </si>
+  <si>
+    <t>Missing Nets</t>
+  </si>
+  <si>
+    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+  </si>
+  <si>
     <t>XGPI,XMAIN</t>
-  </si>
-  <si>
-    <t>XGPI,XMAIN,XNC0.noconn net started as 0 (zero).</t>
-  </si>
-  <si>
-    <t>Validate no "text" in Datamaps</t>
-  </si>
-  <si>
-    <t>No errors</t>
-  </si>
-  <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>No missing bio or symbol files...</t>
-  </si>
-  <si>
-    <t>Missing Nets</t>
-  </si>
-  <si>
-    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
   </si>
   <si>
     <t>XU8,SIMPV</t>
@@ -1034,10 +1037,10 @@
     <t>14</t>
   </si>
   <si>
+    <t>nand2</t>
+  </si>
+  <si>
     <t>noconn</t>
-  </si>
-  <si>
-    <t>nand2</t>
   </si>
   <si>
     <t>wrapper</t>
@@ -1576,7 +1579,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1596,7 +1599,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1616,7 +1619,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1631,7 +1634,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1649,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1666,12 +1669,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1686,12 +1689,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1706,12 +1709,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1726,7 +1729,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1746,127 +1749,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1881,7 +1884,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1926,17 +1929,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1951,7 +1954,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1971,17 +1974,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1996,17 +1999,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2021,81 +2024,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" t="s">
         <v>71</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
         <v>74</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" t="s">
         <v>79</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -2103,185 +2106,185 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B39" t="s">
         <v>1</v>
@@ -2289,445 +2292,445 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B47" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B48" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B49" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B50" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B51" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B54" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B55" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B63" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B66" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B67" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B76" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B77" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B78" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B79" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B80" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B81" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B82" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B83" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B84" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B85" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B86" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B87" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B88" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B89" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B90" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B91" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B92" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B93" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B94" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B95" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B96" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B97" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B98" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B99" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -2735,628 +2738,628 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B101" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B105" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B106" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B107" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B108" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B109" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B110" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B111" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B112" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B115" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B116" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B117" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B118" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B119" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B120" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B121" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B122" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B123" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B124" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B125" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B126" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B127" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B128" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B129" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B130" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B131" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B132" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B133" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B134" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B135" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B136" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B137" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B138" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B139" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B140" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B141" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B142" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B143" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B144" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B145" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B146" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B147" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B148" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B149" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B150" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B151" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B152" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B153" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B154" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B155" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B156" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B157" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B158" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B159" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B160" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B161" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B162" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B163" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B164" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B165" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B166" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B167" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B168" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B169" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B170" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B171" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B172" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B173" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B174" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B175" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B176" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B177" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B178" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B179" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3371,47 +3374,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -3419,15 +3422,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -3435,7 +3438,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -3450,7 +3453,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -3465,26 +3468,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3499,7 +3502,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3509,122 +3512,122 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B8" t="s">
-        <v>308</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B15" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B16" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B17" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B18" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3639,85 +3642,85 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E5" t="s">
+        <v>347</v>
+      </c>
+      <c r="F5" t="s">
+        <v>348</v>
+      </c>
+      <c r="G5" t="s">
+        <v>349</v>
+      </c>
+      <c r="H5" t="s">
+        <v>350</v>
+      </c>
+      <c r="I5" t="s">
         <v>345</v>
       </c>
-      <c r="E5" t="s">
-        <v>346</v>
-      </c>
-      <c r="F5" t="s">
-        <v>347</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="J5" t="s">
+        <v>351</v>
+      </c>
+      <c r="K5" t="s">
         <v>348</v>
       </c>
-      <c r="H5" t="s">
-        <v>349</v>
-      </c>
-      <c r="I5" t="s">
-        <v>344</v>
-      </c>
-      <c r="J5" t="s">
-        <v>350</v>
-      </c>
-      <c r="K5" t="s">
-        <v>347</v>
-      </c>
       <c r="L5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="R5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -3757,22 +3760,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -3787,22 +3790,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -3817,44 +3820,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -3869,44 +3872,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -3921,22 +3924,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -3951,7 +3954,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -3966,7 +3969,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -3981,12 +3984,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -3996,12 +3999,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -4016,7 +4019,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -4031,7 +4034,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -4061,17 +4064,17 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -4086,12 +4089,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -4101,7 +4104,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -4116,7 +4119,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4126,7 +4129,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -4141,7 +4144,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4151,7 +4154,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -4166,7 +4169,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4176,7 +4179,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -4191,7 +4194,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4201,7 +4204,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -4216,7 +4219,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/GPIpuget/project/Address.xlsx
+++ b/GPIpuget/project/Address.xlsx
@@ -413,7 +413,7 @@
     <t>project_netlist_path</t>
   </si>
   <si>
-    <t>/tmp/GPIpuget.net</t>
+    <t>/portal/web/api/utils/hopper/tests/GPIpuget.net</t>
   </si>
   <si>
     <t>gen_reports</t>
